--- a/hira_material_automation/output/monthly/202601_202610__nonmetal_anchor__040019__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202610__nonmetal_anchor__040019__normalized.xlsx
@@ -822,7 +822,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-04T23:53:16</t>
+          <t>2026-10-14T23:46:48</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>69cf3cb6a222c83ba918877cd33ba655b9fd3247e0dae38e55d2e4940b0cd913</t>
+          <t>5fe0fec6218c11ff0c0e2882acf0d8956cd1769bd78c37c7d90054b3dc058b27</t>
         </is>
       </c>
     </row>
